--- a/Excel/LegacySetConfig.xlsx
+++ b/Excel/LegacySetConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -50,6 +55,9 @@
     <t>AtrVueList</t>
   </si>
   <si>
+    <t>RequireList</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -65,22 +73,25 @@
     <t>传世圣战</t>
   </si>
   <si>
-    <t>1004,2004,27,94</t>
-  </si>
-  <si>
-    <t>5,1,1,1</t>
+    <t>1004,2004,27,94,10001</t>
+  </si>
+  <si>
+    <t>5,1,1,1,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0,30</t>
   </si>
   <si>
     <t>传世法神</t>
   </si>
   <si>
-    <t>1005,2005,27,94</t>
+    <t>1005,2005,27,94,10001</t>
   </si>
   <si>
     <t>传世天尊</t>
   </si>
   <si>
-    <t>1006,2006,27,94</t>
+    <t>1006,2006,27,94,10001</t>
   </si>
 </sst>
 </file>
@@ -713,11 +724,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1051,259 +1066,285 @@
     <col min="7" max="7" width="12.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.6666666666667" style="2" customWidth="1"/>
     <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="16365" width="9" style="2"/>
+    <col min="10" max="10" width="16.5833333333333" style="3" customWidth="1"/>
+    <col min="11" max="16365" width="9" style="2"/>
     <col min="16366" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="J3" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:9">
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="D5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="H5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="6">
         <v>1</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="6">
         <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:9">
+      <c r="I6" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="6">
         <v>1</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="6">
         <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="J7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:9">
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1">
         <v>3</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="6">
         <v>1</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="6">
         <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1"/>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1"/>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="5:6">
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1"/>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:7 16366:16382">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="5:10">
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:10 16366:16382">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
+      <c r="J33" s="3"/>
       <c r="XEL33" s="1"/>
       <c r="XEM33" s="1"/>
       <c r="XEN33" s="1"/>
@@ -1322,12 +1363,13 @@
       <c r="XFA33" s="1"/>
       <c r="XFB33" s="1"/>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:7 16366:16382">
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:10 16366:16382">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
+      <c r="J34" s="3"/>
       <c r="XEL34" s="1"/>
       <c r="XEM34" s="1"/>
       <c r="XEN34" s="1"/>
@@ -1346,12 +1388,13 @@
       <c r="XFA34" s="1"/>
       <c r="XFB34" s="1"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:7 16366:16382">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:10 16366:16382">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
+      <c r="J35" s="3"/>
       <c r="XEL35" s="1"/>
       <c r="XEM35" s="1"/>
       <c r="XEN35" s="1"/>

--- a/Excel/LegacySetConfig.xlsx
+++ b/Excel/LegacySetConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -40,12 +40,6 @@
     <t>Role</t>
   </si>
   <si>
-    <t>StartLevel</t>
-  </si>
-  <si>
-    <t>EndLevel</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -55,7 +49,13 @@
     <t>AtrVueList</t>
   </si>
   <si>
-    <t>RequireList</t>
+    <t>SpeIdList</t>
+  </si>
+  <si>
+    <t>SpeVueList</t>
+  </si>
+  <si>
+    <t>SpeRequireList</t>
   </si>
   <si>
     <t>Id</t>
@@ -73,25 +73,31 @@
     <t>传世圣战</t>
   </si>
   <si>
-    <t>1004,2004,27,94,10001</t>
-  </si>
-  <si>
-    <t>5,1,1,1,1</t>
-  </si>
-  <si>
-    <t>0,0,0,0,30</t>
+    <t>1004,2004,27,94</t>
+  </si>
+  <si>
+    <t>5,1,1,1</t>
+  </si>
+  <si>
+    <t>10001,10002</t>
+  </si>
+  <si>
+    <t>10,10</t>
+  </si>
+  <si>
+    <t>25,50</t>
   </si>
   <si>
     <t>传世法神</t>
   </si>
   <si>
-    <t>1005,2005,27,94,10001</t>
+    <t>1005,2005,27,94</t>
   </si>
   <si>
     <t>传世天尊</t>
   </si>
   <si>
-    <t>1006,2006,27,94,10001</t>
+    <t>1006,2006,27,94</t>
   </si>
 </sst>
 </file>
@@ -724,19 +730,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1056,116 +1058,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFB35"/>
+  <dimension ref="A1:XFA35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.6666666666667" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17" style="2" customWidth="1"/>
-    <col min="10" max="10" width="16.5833333333333" style="3" customWidth="1"/>
-    <col min="11" max="16365" width="9" style="2"/>
-    <col min="16366" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="12.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.6666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.9166666666667" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="2" customWidth="1"/>
+    <col min="11" max="16364" width="9" style="2"/>
+    <col min="16365" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="3"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="3"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1176,23 +1183,23 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="F6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="H6" s="5" t="s">
         <v>15</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1202,23 +1209,23 @@
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="J7" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:10">
@@ -1228,123 +1235,150 @@
       <c r="D8" s="1">
         <v>3</v>
       </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6">
-        <v>10</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="7" t="s">
+      <c r="E8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="H8" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="I8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+    </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="5:10">
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:10 16366:16382">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="8:10">
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+    </row>
+    <row r="33" s="2" customFormat="1" customHeight="1" spans="3:5 16365:16381">
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="J33" s="3"/>
+      <c r="XEK33" s="1"/>
       <c r="XEL33" s="1"/>
       <c r="XEM33" s="1"/>
       <c r="XEN33" s="1"/>
@@ -1361,15 +1395,12 @@
       <c r="XEY33" s="1"/>
       <c r="XEZ33" s="1"/>
       <c r="XFA33" s="1"/>
-      <c r="XFB33" s="1"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:10 16366:16382">
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:5 16365:16381">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="J34" s="3"/>
+      <c r="XEK34" s="1"/>
       <c r="XEL34" s="1"/>
       <c r="XEM34" s="1"/>
       <c r="XEN34" s="1"/>
@@ -1386,15 +1417,12 @@
       <c r="XEY34" s="1"/>
       <c r="XEZ34" s="1"/>
       <c r="XFA34" s="1"/>
-      <c r="XFB34" s="1"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:10 16366:16382">
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:5 16365:16381">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="J35" s="3"/>
+      <c r="XEK35" s="1"/>
       <c r="XEL35" s="1"/>
       <c r="XEM35" s="1"/>
       <c r="XEN35" s="1"/>
@@ -1411,11 +1439,10 @@
       <c r="XEY35" s="1"/>
       <c r="XEZ35" s="1"/>
       <c r="XFA35" s="1"/>
-      <c r="XFB35" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
